--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
 (25年-04月-11日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 448呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -2173,23 +2173,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>27902</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2198,12 +2194,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2213,7 +2209,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6115,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6129,7 +6125,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6410,12 +6406,12 @@
 (25年-04月-11日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 448呎 (2房)
-招标单位
--
-(在售)</t>
+$1250万
+$27,902/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 671呎 (3房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -2178,7 +2178,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -6411,7 +6411,7 @@
           <t>E | 448呎 (2房)
 $1250万
 $27,902/呎
-(26年-09月-13日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">

--- a/files/九龙-何文田-名钻.xlsx
+++ b/files/九龙-何文田-名钻.xlsx
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>16562000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>24646</v>
+        <v>24683</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>15853000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>23591</v>
+        <v>23626</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>15391000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>22903</v>
+        <v>22937</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>15246000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>22688</v>
+        <v>22721</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>14802000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>22027</v>
+        <v>22060</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>14301000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>21281</v>
+        <v>21313</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>13844000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>20601</v>
+        <v>20632</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>13558000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>20176</v>
+        <v>20206</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>13262000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>19735</v>
+        <v>19765</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>12962000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>19289</v>
+        <v>19317</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -6416,9 +6416,9 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1656万
-$24,646/呎
+$24,683/呎
 (25年-07月-18日)</t>
         </is>
       </c>
@@ -6471,9 +6471,9 @@
       </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1585万
-$23,591/呎
+$23,626/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -6526,9 +6526,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1539万
-$22,903/呎
+$22,937/呎
 (26年-01月-02日)</t>
         </is>
       </c>
@@ -6581,9 +6581,9 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1525万
-$22,688/呎
+$22,721/呎
 (26年-01月-29日)</t>
         </is>
       </c>
@@ -6636,9 +6636,9 @@
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1480万
-$22,027/呎
+$22,060/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -6691,9 +6691,9 @@
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1430万
-$21,281/呎
+$21,313/呎
 (26年-01月-20日)</t>
         </is>
       </c>
@@ -6746,9 +6746,9 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1384万
-$20,601/呎
+$20,632/呎
 (25年-12月-02日)</t>
         </is>
       </c>
@@ -6801,9 +6801,9 @@
       </c>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1356万
-$20,176/呎
+$20,206/呎
 (26年-01月-02日)</t>
         </is>
       </c>
@@ -6856,9 +6856,9 @@
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1326万
-$19,735/呎
+$19,765/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -6911,9 +6911,9 @@
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>F | 672呎 (3房)
+          <t>F | 671呎 (3房)
 $1296万
-$19,289/呎
+$19,317/呎
 (24年-12月-24日)</t>
         </is>
       </c>
